--- a/Groups.xlsx
+++ b/Groups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Kent Institute\Terms\T2-2026\CPRO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27ABE5F-DDBE-4981-B4EB-1BA6BA1AF3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B4C1AB-FA07-4631-B326-BECB823F383F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{828F6794-54D3-47BF-9476-C358D9B958EA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
   <si>
     <t>Student ID</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Group 2</t>
   </si>
   <si>
@@ -111,6 +108,114 @@
   </si>
   <si>
     <t>Project</t>
+  </si>
+  <si>
+    <t>Mr Sujan Darji</t>
+  </si>
+  <si>
+    <t>K231673</t>
+  </si>
+  <si>
+    <t>Mr Shaurav Khadka</t>
+  </si>
+  <si>
+    <t>K230869</t>
+  </si>
+  <si>
+    <t>Mr Amrit Rimal</t>
+  </si>
+  <si>
+    <t>K240619</t>
+  </si>
+  <si>
+    <t>Mr Santosh Budha</t>
+  </si>
+  <si>
+    <t>K231815</t>
+  </si>
+  <si>
+    <t>Anthony Allan Regalado</t>
+  </si>
+  <si>
+    <t>not enrolled yet</t>
+  </si>
+  <si>
+    <t>Mr Russel Carlo Cabrera</t>
+  </si>
+  <si>
+    <t>K230618</t>
+  </si>
+  <si>
+    <t>Ms Roselle Joy Iracta</t>
+  </si>
+  <si>
+    <t>K231518</t>
+  </si>
+  <si>
+    <t>Ms Mikaela Montano</t>
+  </si>
+  <si>
+    <t>K230241</t>
+  </si>
+  <si>
+    <t>Mr Alex Dware</t>
+  </si>
+  <si>
+    <t>K240698</t>
+  </si>
+  <si>
+    <t>Mr Karambir Chaudhary</t>
+  </si>
+  <si>
+    <t>K240854</t>
+  </si>
+  <si>
+    <t>Mr Anuj Kamboj</t>
+  </si>
+  <si>
+    <t>K231936</t>
+  </si>
+  <si>
+    <t>Ms Krishala Thapa</t>
+  </si>
+  <si>
+    <t>K241031</t>
+  </si>
+  <si>
+    <t>Ms Lai Kun Mak</t>
+  </si>
+  <si>
+    <t>K240715</t>
+  </si>
+  <si>
+    <t>Mr Louis Surya</t>
+  </si>
+  <si>
+    <t>K240169</t>
+  </si>
+  <si>
+    <t>Mr William Veleda</t>
+  </si>
+  <si>
+    <t>K231904</t>
+  </si>
+  <si>
+    <t>Mr Petrick Pun Magar</t>
+  </si>
+  <si>
+    <t>K240465</t>
+  </si>
+  <si>
+    <t>Mr Shalik Ram Dhakal</t>
+  </si>
+  <si>
+    <t>K240466</t>
+  </si>
+  <si>
+    <t>Mr Bed Prakash Mahato</t>
+  </si>
+  <si>
+    <t>K240559</t>
   </si>
 </sst>
 </file>
@@ -610,44 +715,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{265F12A5-6B01-429C-9211-C9526CC420E7}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="17" t="s">
         <v>22</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>23</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>0</v>
@@ -669,17 +774,21 @@
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="18" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>15</v>
       </c>
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
@@ -691,38 +800,38 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="F3" s="4"/>
       <c r="H3" s="19"/>
       <c r="I3" s="19"/>
       <c r="J3" s="19"/>
       <c r="K3" s="19"/>
       <c r="L3" s="19"/>
-      <c r="M3" s="19" t="s">
-        <v>7</v>
-      </c>
+      <c r="M3" s="19"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="F4" s="4"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
-      <c r="M4" s="19" t="s">
-        <v>7</v>
-      </c>
+      <c r="M4" s="19"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
@@ -730,17 +839,13 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
       <c r="L5" s="19"/>
-      <c r="M5" s="19" t="s">
-        <v>7</v>
-      </c>
+      <c r="M5" s="19"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
@@ -748,17 +853,13 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="F6" s="4"/>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
-      <c r="M6" s="19" t="s">
-        <v>7</v>
-      </c>
+      <c r="M6" s="19"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -776,10 +877,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -788,13 +889,17 @@
         <v>6</v>
       </c>
       <c r="H8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="J8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>41</v>
+      </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12" t="s">
         <v>6</v>
@@ -806,17 +911,17 @@
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
-        <v>7</v>
-      </c>
+      <c r="F9" s="6"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
+      <c r="J9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="L9" s="12"/>
-      <c r="M9" s="12" t="s">
-        <v>7</v>
-      </c>
+      <c r="M9" s="12"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
@@ -824,17 +929,13 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="6" t="s">
-        <v>7</v>
-      </c>
+      <c r="F10" s="6"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
       <c r="L10" s="12"/>
-      <c r="M10" s="12" t="s">
-        <v>7</v>
-      </c>
+      <c r="M10" s="12"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
@@ -842,17 +943,13 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="6" t="s">
-        <v>7</v>
-      </c>
+      <c r="F11" s="6"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
       <c r="L11" s="12"/>
-      <c r="M11" s="12" t="s">
-        <v>7</v>
-      </c>
+      <c r="M11" s="12"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
@@ -860,17 +957,13 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="6" t="s">
-        <v>7</v>
-      </c>
+      <c r="F12" s="6"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
       <c r="L12" s="12"/>
-      <c r="M12" s="12" t="s">
-        <v>7</v>
-      </c>
+      <c r="M12" s="12"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -888,25 +981,33 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
         <v>6</v>
       </c>
       <c r="H14" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
+      <c r="J14" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="L14" s="14"/>
       <c r="M14" s="14" t="s">
         <v>6</v>
@@ -915,76 +1016,93 @@
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="C15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
-        <v>7</v>
-      </c>
+      <c r="F15" s="8"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
+      <c r="J15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="L15" s="14"/>
-      <c r="M15" s="14" t="s">
-        <v>7</v>
-      </c>
+      <c r="M15" s="14"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="C16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
-        <v>7</v>
-      </c>
+      <c r="F16" s="8"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
+      <c r="J16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="L16" s="14"/>
-      <c r="M16" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M16" s="14"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="C17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
-        <v>7</v>
-      </c>
+      <c r="F17" s="8"/>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
+      <c r="J17" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="L17" s="14"/>
-      <c r="M17" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="14"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
-        <v>7</v>
-      </c>
+      <c r="F18" s="8"/>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
+      <c r="K18" s="14" t="s">
+        <v>31</v>
+      </c>
       <c r="L18" s="14"/>
-      <c r="M18" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M18" s="14"/>
+      <c r="N18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -998,24 +1116,28 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
+      <c r="C20" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10" t="s">
         <v>6</v>
       </c>
       <c r="H20" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="15" t="s">
         <v>20</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>21</v>
       </c>
       <c r="J20" s="16"/>
       <c r="K20" s="16"/>
@@ -1024,79 +1146,71 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
+      <c r="C21" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="E21" s="10"/>
-      <c r="F21" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="F21" s="10"/>
       <c r="H21" s="16"/>
       <c r="I21" s="16"/>
       <c r="J21" s="16"/>
       <c r="K21" s="16"/>
       <c r="L21" s="16"/>
-      <c r="M21" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M21" s="16"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
+      <c r="C22" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="E22" s="10"/>
-      <c r="F22" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="F22" s="10"/>
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
-      <c r="M22" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M22" s="16"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="F23" s="10"/>
       <c r="H23" s="16"/>
       <c r="I23" s="16"/>
       <c r="J23" s="16"/>
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
-      <c r="M23" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M23" s="16"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="F24" s="10"/>
       <c r="H24" s="16"/>
       <c r="I24" s="16"/>
       <c r="J24" s="16"/>
       <c r="K24" s="16"/>
       <c r="L24" s="16"/>
-      <c r="M24" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M24" s="16"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1106,5 +1220,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>